--- a/plugins/sanity-check/skills/sanity-check/evals/pack-2026-11-dirty.xlsx
+++ b/plugins/sanity-check/skills/sanity-check/evals/pack-2026-11-dirty.xlsx
@@ -439,13 +439,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -499,6 +501,13 @@
       <c r="D5" t="n">
         <v>66</v>
       </c>
+      <c r="E5" t="n">
+        <v>1800</v>
+      </c>
+      <c r="F5">
+        <f>B5-E5</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -515,6 +524,13 @@
       <c r="D6" t="n">
         <v>30</v>
       </c>
+      <c r="E6" t="n">
+        <v>900</v>
+      </c>
+      <c r="F6">
+        <f>B6-E6</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -531,6 +547,13 @@
       <c r="D7" t="n">
         <v>15</v>
       </c>
+      <c r="E7" t="n">
+        <v>450</v>
+      </c>
+      <c r="F7">
+        <f>B7-E7</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -548,6 +571,13 @@
       </c>
       <c r="D8" s="3" t="n">
         <v>113</v>
+      </c>
+      <c r="E8" s="3">
+        <f>SUM(E5:E7)</f>
+        <v/>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>56</v>
       </c>
     </row>
     <row r="10">

--- a/plugins/sanity-check/skills/sanity-check/evals/pack-2026-11-dirty.xlsx
+++ b/plugins/sanity-check/skills/sanity-check/evals/pack-2026-11-dirty.xlsx
@@ -485,6 +485,16 @@
           <t>Headcount</t>
         </is>
       </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Plan (£000s)</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Var to plan</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
